--- a/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ORBT_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="92">
   <si>
     <t>ORBT</t>
   </si>
@@ -819,8 +819,8 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>8</v>
+      <c r="D8" s="3">
+        <v>5200</v>
       </c>
       <c r="E8" s="3">
         <v>4700</v>
@@ -828,8 +828,8 @@
       <c r="F8" s="3">
         <v>8700</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>8</v>
+      <c r="G8" s="3">
+        <v>8400</v>
       </c>
       <c r="H8" s="3">
         <v>6600</v>
@@ -932,8 +932,8 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>3800</v>
       </c>
       <c r="E9" s="3">
         <v>4100</v>
@@ -941,8 +941,8 @@
       <c r="F9" s="3">
         <v>5700</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>8</v>
+      <c r="G9" s="3">
+        <v>5300</v>
       </c>
       <c r="H9" s="3">
         <v>4700</v>
@@ -1045,8 +1045,8 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3">
+        <v>1400</v>
       </c>
       <c r="E10" s="3">
         <v>600</v>
@@ -1054,8 +1054,8 @@
       <c r="F10" s="3">
         <v>3000</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>8</v>
+      <c r="G10" s="3">
+        <v>3100</v>
       </c>
       <c r="H10" s="3">
         <v>1900</v>
@@ -1539,16 +1539,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E15" s="3">
         <v>200</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H15" s="3">
         <v>200</v>
@@ -1689,8 +1689,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>6400</v>
       </c>
       <c r="E17" s="3">
         <v>6900</v>
@@ -1698,8 +1698,8 @@
       <c r="F17" s="3">
         <v>8400</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>8</v>
+      <c r="G17" s="3">
+        <v>7800</v>
       </c>
       <c r="H17" s="3">
         <v>7200</v>
@@ -1802,8 +1802,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>-1200</v>
       </c>
       <c r="E18" s="3">
         <v>-2100</v>
@@ -1811,8 +1811,8 @@
       <c r="F18" s="3">
         <v>300</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>8</v>
+      <c r="G18" s="3">
+        <v>600</v>
       </c>
       <c r="H18" s="3">
         <v>-600</v>
@@ -1956,8 +1956,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1965,8 +1965,8 @@
       <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>8</v>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>-400</v>
@@ -2070,16 +2070,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>-1100</v>
       </c>
       <c r="E21" s="3">
         <v>-2000</v>
       </c>
       <c r="F21" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G21" s="3">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="H21" s="3">
         <v>0</v>
@@ -2182,8 +2182,8 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>0</v>
       </c>
       <c r="E22" s="3">
         <v>0</v>
@@ -2191,8 +2191,8 @@
       <c r="F22" s="3">
         <v>100</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
         <v>0</v>
@@ -2295,8 +2295,8 @@
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>8</v>
+      <c r="D23" s="3">
+        <v>-1300</v>
       </c>
       <c r="E23" s="3">
         <v>-2100</v>
@@ -2304,8 +2304,8 @@
       <c r="F23" s="3">
         <v>200</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>8</v>
+      <c r="G23" s="3">
+        <v>600</v>
       </c>
       <c r="H23" s="3">
         <v>-200</v>
@@ -2408,8 +2408,8 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>8</v>
+      <c r="D24" s="3">
+        <v>0</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -2634,8 +2634,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>-1300</v>
       </c>
       <c r="E26" s="3">
         <v>-2200</v>
@@ -2643,8 +2643,8 @@
       <c r="F26" s="3">
         <v>-300</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>8</v>
+      <c r="G26" s="3">
+        <v>600</v>
       </c>
       <c r="H26" s="3">
         <v>-200</v>
@@ -2747,8 +2747,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>-1300</v>
       </c>
       <c r="E27" s="3">
         <v>-2200</v>
@@ -2756,8 +2756,8 @@
       <c r="F27" s="3">
         <v>-300</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>8</v>
+      <c r="G27" s="3">
+        <v>600</v>
       </c>
       <c r="H27" s="3">
         <v>-200</v>
@@ -3312,8 +3312,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -3321,8 +3321,8 @@
       <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>8</v>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>400</v>
@@ -3425,8 +3425,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>-1300</v>
       </c>
       <c r="E33" s="3">
         <v>-2200</v>
@@ -3434,8 +3434,8 @@
       <c r="F33" s="3">
         <v>-300</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>8</v>
+      <c r="G33" s="3">
+        <v>600</v>
       </c>
       <c r="H33" s="3">
         <v>-200</v>
@@ -3651,8 +3651,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>-1300</v>
       </c>
       <c r="E35" s="3">
         <v>-2200</v>
@@ -3660,8 +3660,8 @@
       <c r="F35" s="3">
         <v>-300</v>
       </c>
-      <c r="G35" s="3" t="s">
-        <v>8</v>
+      <c r="G35" s="3">
+        <v>600</v>
       </c>
       <c r="H35" s="3">
         <v>-200</v>
@@ -3964,8 +3964,8 @@
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>8</v>
+      <c r="D41" s="3">
+        <v>400</v>
       </c>
       <c r="E41" s="3">
         <v>700</v>
@@ -3973,8 +3973,8 @@
       <c r="F41" s="3">
         <v>1400</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>8</v>
+      <c r="G41" s="3">
+        <v>300</v>
       </c>
       <c r="H41" s="3">
         <v>500</v>
@@ -4190,8 +4190,8 @@
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>8</v>
+      <c r="D43" s="3">
+        <v>3200</v>
       </c>
       <c r="E43" s="3">
         <v>3200</v>
@@ -4199,8 +4199,8 @@
       <c r="F43" s="3">
         <v>4600</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>8</v>
+      <c r="G43" s="3">
+        <v>5300</v>
       </c>
       <c r="H43" s="3">
         <v>4300</v>
@@ -4303,8 +4303,8 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>8</v>
+      <c r="D44" s="3">
+        <v>9200</v>
       </c>
       <c r="E44" s="3">
         <v>9100</v>
@@ -4312,8 +4312,8 @@
       <c r="F44" s="3">
         <v>8900</v>
       </c>
-      <c r="G44" s="3" t="s">
-        <v>8</v>
+      <c r="G44" s="3">
+        <v>10400</v>
       </c>
       <c r="H44" s="3">
         <v>10300</v>
@@ -4416,8 +4416,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>300</v>
       </c>
       <c r="E45" s="3">
         <v>400</v>
@@ -4425,8 +4425,8 @@
       <c r="F45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
+      <c r="G45" s="3">
+        <v>400</v>
       </c>
       <c r="H45" s="3">
         <v>400</v>
@@ -4529,8 +4529,8 @@
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>8</v>
+      <c r="D46" s="3">
+        <v>13200</v>
       </c>
       <c r="E46" s="3">
         <v>13300</v>
@@ -4538,8 +4538,8 @@
       <c r="F46" s="3">
         <v>15200</v>
       </c>
-      <c r="G46" s="3" t="s">
-        <v>8</v>
+      <c r="G46" s="3">
+        <v>16400</v>
       </c>
       <c r="H46" s="3">
         <v>15500</v>
@@ -4755,8 +4755,8 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>8</v>
+      <c r="D48" s="3">
+        <v>3100</v>
       </c>
       <c r="E48" s="3">
         <v>3300</v>
@@ -4764,8 +4764,8 @@
       <c r="F48" s="3">
         <v>3600</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>8</v>
+      <c r="G48" s="3">
+        <v>3300</v>
       </c>
       <c r="H48" s="3">
         <v>3600</v>
@@ -4868,8 +4868,8 @@
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>8</v>
+      <c r="D49" s="3">
+        <v>5700</v>
       </c>
       <c r="E49" s="3">
         <v>5800</v>
@@ -4877,8 +4877,8 @@
       <c r="F49" s="3">
         <v>5800</v>
       </c>
-      <c r="G49" s="3" t="s">
-        <v>8</v>
+      <c r="G49" s="3">
+        <v>5900</v>
       </c>
       <c r="H49" s="3">
         <v>6000</v>
@@ -5207,8 +5207,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
@@ -5216,8 +5216,8 @@
       <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>8</v>
+      <c r="G52" s="3">
+        <v>100</v>
       </c>
       <c r="H52" s="3">
         <v>100</v>
@@ -5433,8 +5433,8 @@
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>8</v>
+      <c r="D54" s="3">
+        <v>22200</v>
       </c>
       <c r="E54" s="3">
         <v>22600</v>
@@ -5442,8 +5442,8 @@
       <c r="F54" s="3">
         <v>24800</v>
       </c>
-      <c r="G54" s="3" t="s">
-        <v>8</v>
+      <c r="G54" s="3">
+        <v>26200</v>
       </c>
       <c r="H54" s="3">
         <v>25700</v>
@@ -5628,8 +5628,8 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>8</v>
+      <c r="D57" s="3">
+        <v>1000</v>
       </c>
       <c r="E57" s="3">
         <v>1000</v>
@@ -5637,8 +5637,8 @@
       <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="G57" s="3" t="s">
-        <v>8</v>
+      <c r="G57" s="3">
+        <v>1400</v>
       </c>
       <c r="H57" s="3">
         <v>1400</v>
@@ -5741,8 +5741,8 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>8</v>
+      <c r="D58" s="3">
+        <v>2500</v>
       </c>
       <c r="E58" s="3">
         <v>1700</v>
@@ -5750,8 +5750,8 @@
       <c r="F58" s="3">
         <v>1700</v>
       </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
+      <c r="G58" s="3">
+        <v>1700</v>
       </c>
       <c r="H58" s="3">
         <v>1200</v>
@@ -5854,8 +5854,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>1800</v>
       </c>
       <c r="E59" s="3">
         <v>1600</v>
@@ -5863,8 +5863,8 @@
       <c r="F59" s="3">
         <v>1700</v>
       </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
+      <c r="G59" s="3">
+        <v>2100</v>
       </c>
       <c r="H59" s="3">
         <v>2400</v>
@@ -5967,8 +5967,8 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>8</v>
+      <c r="D60" s="3">
+        <v>6400</v>
       </c>
       <c r="E60" s="3">
         <v>5400</v>
@@ -5976,8 +5976,8 @@
       <c r="F60" s="3">
         <v>5200</v>
       </c>
-      <c r="G60" s="3" t="s">
-        <v>8</v>
+      <c r="G60" s="3">
+        <v>6300</v>
       </c>
       <c r="H60" s="3">
         <v>6100</v>
@@ -6081,7 +6081,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E61" s="3">
         <v>1600</v>
@@ -6090,7 +6090,7 @@
         <v>1800</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H61" s="3">
         <v>2000</v>
@@ -6202,8 +6202,8 @@
       <c r="F62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="3" t="s">
-        <v>8</v>
+      <c r="G62" s="3">
+        <v>0</v>
       </c>
       <c r="H62" s="3">
         <v>0</v>
@@ -6645,8 +6645,8 @@
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>8</v>
+      <c r="D66" s="3">
+        <v>7800</v>
       </c>
       <c r="E66" s="3">
         <v>7000</v>
@@ -6654,8 +6654,8 @@
       <c r="F66" s="3">
         <v>7000</v>
       </c>
-      <c r="G66" s="3" t="s">
-        <v>8</v>
+      <c r="G66" s="3">
+        <v>8100</v>
       </c>
       <c r="H66" s="3">
         <v>8100</v>
@@ -7251,8 +7251,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>-2000</v>
       </c>
       <c r="E72" s="3">
         <v>-700</v>
@@ -7260,8 +7260,8 @@
       <c r="F72" s="3">
         <v>1500</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>8</v>
+      <c r="G72" s="3">
+        <v>1700</v>
       </c>
       <c r="H72" s="3">
         <v>1200</v>
@@ -7703,8 +7703,8 @@
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>8</v>
+      <c r="D76" s="3">
+        <v>14300</v>
       </c>
       <c r="E76" s="3">
         <v>15600</v>
@@ -7712,8 +7712,8 @@
       <c r="F76" s="3">
         <v>17800</v>
       </c>
-      <c r="G76" s="3" t="s">
-        <v>8</v>
+      <c r="G76" s="3">
+        <v>18100</v>
       </c>
       <c r="H76" s="3">
         <v>17500</v>
@@ -8047,8 +8047,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>-1300</v>
       </c>
       <c r="E81" s="3">
         <v>-2200</v>
@@ -8056,8 +8056,8 @@
       <c r="F81" s="3">
         <v>-300</v>
       </c>
-      <c r="G81" s="3" t="s">
-        <v>8</v>
+      <c r="G81" s="3">
+        <v>600</v>
       </c>
       <c r="H81" s="3">
         <v>-200</v>
@@ -8202,16 +8202,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>8</v>
+      <c r="F83" s="3">
+        <v>500</v>
+      </c>
+      <c r="G83" s="3">
+        <v>100</v>
       </c>
       <c r="H83" s="3">
         <v>100</v>
@@ -8879,17 +8879,17 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>-1000</v>
       </c>
       <c r="E89" s="3">
         <v>-600</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>8</v>
+      <c r="F89" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-600</v>
       </c>
       <c r="H89" s="3">
         <v>-1500</v>
@@ -8897,8 +8897,8 @@
       <c r="I89" s="3">
         <v>700</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>8</v>
+      <c r="J89" s="3">
+        <v>1400</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>8</v>
@@ -9033,17 +9033,17 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
-      <c r="F91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>8</v>
+      <c r="F91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G91" s="3">
+        <v>0</v>
       </c>
       <c r="H91" s="3">
         <v>0</v>
@@ -9051,8 +9051,8 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>8</v>
+      <c r="J91" s="3">
+        <v>-200</v>
       </c>
       <c r="K91" s="3" t="s">
         <v>8</v>
@@ -9372,17 +9372,17 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>0</v>
       </c>
       <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>8</v>
+      <c r="F94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G94" s="3">
+        <v>0</v>
       </c>
       <c r="H94" s="3">
         <v>0</v>
@@ -9390,8 +9390,8 @@
       <c r="I94" s="3">
         <v>0</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>8</v>
+      <c r="J94" s="3">
+        <v>-200</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>8</v>
@@ -9532,11 +9532,11 @@
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>8</v>
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3">
+        <v>0</v>
       </c>
       <c r="H96" s="3">
         <v>0</v>
@@ -9544,8 +9544,8 @@
       <c r="I96" s="3">
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>8</v>
+      <c r="J96" s="3">
+        <v>0</v>
       </c>
       <c r="K96" s="3" t="s">
         <v>8</v>
@@ -9978,17 +9978,17 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>700</v>
       </c>
       <c r="E100" s="3">
         <v>0</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>8</v>
+      <c r="F100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G100" s="3">
+        <v>500</v>
       </c>
       <c r="H100" s="3">
         <v>100</v>
@@ -9996,8 +9996,8 @@
       <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>8</v>
+      <c r="J100" s="3">
+        <v>-900</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>8</v>
@@ -10205,16 +10205,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E102" s="3">
         <v>-700</v>
       </c>
       <c r="F102" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H102" s="3">
         <v>-1400</v>
@@ -10223,7 +10223,7 @@
         <v>600</v>
       </c>
       <c r="J102" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
